--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T10:31:14+00:00</t>
+    <t>2026-02-04T11:03:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T11:03:32+00:00</t>
+    <t>2026-02-06T08:16:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T08:16:26+00:00</t>
+    <t>2026-02-06T09:56:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T09:56:58+00:00</t>
+    <t>2026-02-06T10:49:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Goal|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Goal</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -623,11 +623,11 @@
     <t>referenceEvaluation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-evaluation-reference|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-evaluation-reference}
 </t>
   </si>
   <si>
-    <t>Lien vers l'évaluation</t>
+    <t>TDDUI Evaluation Ref</t>
   </si>
   <si>
     <t>Liens vers l'évaluation, utilisables dans le profil TDDUIGoalObjectif.</t>
@@ -646,11 +646,11 @@
     <t>referenceProjetPerso</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-careplan-reference}
 </t>
   </si>
   <si>
-    <t>Lien vers le projet personnalisé</t>
+    <t>TDDUI CarePlan Projet Perso Ref</t>
   </si>
   <si>
     <t>Liens vers le projet personnalisé, utilisables dans le profil TDDUIGoalObjectif.</t>
@@ -665,11 +665,11 @@
     <t>pieceJointeObjectif</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-attachment}
 </t>
   </si>
   <si>
-    <t>Pièce jointe</t>
+    <t>TDDUI Attachment</t>
   </si>
   <si>
     <t>Extension permettant de véhiculer des pièces jointes que ce soit pour l'évaluation, l'évènement ou le projet personnalisé. L'extension référence le profil PDSm_SimplifiedPublish.</t>
@@ -938,11 +938,11 @@
     <t>auteurStatut</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-status-author}
 </t>
   </si>
   <si>
-    <t>TDDUI Auteur statut</t>
+    <t>TDDUI Status Author</t>
   </si>
   <si>
     <t>Extension permettant de représenter la profession du professionnel.</t>
@@ -1121,7 +1121,7 @@
     <t>Goal.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-patient-ins)
 </t>
   </si>
   <si>
@@ -1336,7 +1336,7 @@
     <t>Goal.expressedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|2.2.0-ballot|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner-role|https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-practitioner)
 </t>
   </si>
   <si>
@@ -1358,7 +1358,7 @@
     <t>Goal.addresses</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin|2.2.0-ballot)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-service-request-besoin)
 </t>
   </si>
   <si>
@@ -1424,11 +1424,11 @@
     <t>3</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator|2.2.0-ballot}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-discriminator}
 </t>
   </si>
   <si>
-    <t>TDDUI Discriminator Extension</t>
+    <t>TDDUI Discriminator</t>
   </si>
   <si>
     <t>Extension pour discriminer les éléments CarePlan.supportingInfo et Goal.note.</t>
@@ -1559,13 +1559,13 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="titreObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note-vs|2.2.0-ballot</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/tddui/ValueSet/tddui-goal-objectif-note</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -1612,7 +1612,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="avisUsagerObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -1659,7 +1659,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
-    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator-cs"/&gt;
+    &lt;system value="https://interop.esante.gouv.fr/ig/fhir/tddui/CodeSystem/tddui-discriminator"/&gt;
     &lt;code value="strategieMiseEnOeuvreObjectif"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -2020,7 +2020,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="158.5546875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="139.5390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2035,7 +2035,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="131.83984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="60.3203125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="86.6484375" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T10:49:33+00:00</t>
+    <t>2026-02-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-10T10:00:25+00:00</t>
+    <t>2026-02-11T15:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T15:08:15+00:00</t>
+    <t>2026-02-12T14:50:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T14:50:08+00:00</t>
+    <t>2026-02-16T09:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:17:35+00:00</t>
+    <t>2026-02-16T09:32:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T09:32:48+00:00</t>
+    <t>2026-02-16T14:58:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T14:58:48+00:00</t>
+    <t>2026-02-23T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T15:44:46+00:00</t>
+    <t>2026-02-24T10:21:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T10:21:42+00:00</t>
+    <t>2026-02-24T16:53:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-24T16:53:25+00:00</t>
+    <t>2026-02-25T09:45:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0-ballot</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T09:45:56+00:00</t>
+    <t>2026-02-26T08:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
+++ b/417-contenu-fhir---ajout-des-causes-de-décès/ig/StructureDefinition-tddui-goal-objectif.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T08:21:36+00:00</t>
+    <t>2026-02-26T10:20:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -945,7 +945,7 @@
     <t>TDDUI Status Author</t>
   </si>
   <si>
-    <t>Extension permettant de représenter la profession du professionnel.</t>
+    <t>Extension permettant de représenter l'auteur du statut.</t>
   </si>
   <si>
     <t>statutObjectif.auteur</t>
